--- a/LangMod/EN/Quests.xlsx
+++ b/LangMod/EN/Quests.xlsx
@@ -510,8 +510,57 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">I had promised to deliver #2 to my father who lives in #3, but the procurement was delayed, and it looks like I won’t make it in time on foot. Use a return spell, a teleporter, or whatever you need—just hurry and take it to him.
-Damn it, my father in #3 asked me for #2, but it seems I delivered less than he requested. Take the additional amount to him immediately. </t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I had promised to deliver #2 to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">[qClient]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> who lives in #3, but the procurement was delayed, and it looks like I won’t make it in time on foot. Use a return spell, a teleporter, or whatever you need—just hurry and take it to him.
+Damn it, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">[qClient]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> in #3 asked me for #2, but it seems I delivered less than he requested. Take the additional amount to him immediately. </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">byakko_mod_guild_merchant_escort</t>
@@ -4151,7 +4200,7 @@
         <v>92</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>206</v>
@@ -4214,7 +4263,7 @@
         <v>92</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="L30" s="15" t="s">
         <v>214</v>
@@ -4333,7 +4382,7 @@
         <v>92</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>227</v>

--- a/LangMod/EN/Quests.xlsx
+++ b/LangMod/EN/Quests.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="337">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1371,7 +1371,7 @@
   </si>
   <si>
     <t xml:space="preserve">The guild is running a “Let’s Clear a Nefia” campaign. It’s simple — just clear one Nefia anywhere you like. Why not join?
-We’ve received a request from the settlers of Misiria. They’d like Nefias suppressed to increase the number of safe settlement candidates, even if only a little. Clear any Nefia you can find; once you defeat the boss the lesser enemies will scatter on their own. </t>
+We’ve received a request from the settlers of Mysilia. They’d like Nefias suppressed to increase the number of safe settlement candidates, even if only a little. Clear any Nefia you can find; once you defeat the boss the lesser enemies will scatter on their own. </t>
   </si>
   <si>
     <t xml:space="preserve">byakko_mod_guild_fighter_hunt_stronger</t>
@@ -1888,6 +1888,10 @@
       </rPr>
       <t xml:space="preserve">_fighter_dungeon_attack</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The guild is running a “Let’s Clear a Nefia” campaign. It’s simple — just clear one Nefia anywhere you like. Why not join?
+We’ve received a request from the settlers of Misiria. They’d like Nefias suppressed to increase the number of safe settlement candidates, even if only a little. Clear any Nefia you can find; once you defeat the boss the lesser enemies will scatter on their own. </t>
   </si>
   <si>
     <r>
@@ -5104,7 +5108,7 @@
         <v>174</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="9"/>
@@ -5113,16 +5117,16 @@
     </row>
     <row r="38" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="12"/>
@@ -5142,10 +5146,10 @@
         <v>53</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="9"/>
@@ -5154,16 +5158,16 @@
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -5171,19 +5175,19 @@
         <v>173</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="9"/>
@@ -5192,16 +5196,16 @@
     </row>
     <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -5209,7 +5213,7 @@
         <v>26</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>37</v>
@@ -5221,10 +5225,10 @@
         <v>28</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="9"/>
@@ -5233,16 +5237,16 @@
     </row>
     <row r="41" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -5250,7 +5254,7 @@
         <v>26</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>53</v>
@@ -5262,10 +5266,10 @@
         <v>37</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N41" s="3"/>
       <c r="P41" s="9"/>
@@ -5273,16 +5277,16 @@
     </row>
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -5290,7 +5294,7 @@
         <v>26</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>199</v>
@@ -5302,10 +5306,10 @@
         <v>38</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M42" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N42" s="7"/>
       <c r="O42" s="4"/>
@@ -5314,16 +5318,16 @@
     </row>
     <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -5331,7 +5335,7 @@
         <v>26</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>62</v>
@@ -5343,10 +5347,10 @@
         <v>38</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="9"/>
@@ -5355,16 +5359,16 @@
     </row>
     <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -5372,7 +5376,7 @@
         <v>26</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>199</v>
@@ -5384,10 +5388,10 @@
         <v>37</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="4"/>
@@ -5396,16 +5400,16 @@
     </row>
     <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E45" s="9"/>
       <c r="F45" s="12"/>
@@ -5413,7 +5417,7 @@
         <v>26</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>76</v>
@@ -5425,10 +5429,10 @@
         <v>148</v>
       </c>
       <c r="L45" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="9"/>
@@ -5437,16 +5441,16 @@
     </row>
     <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -5454,7 +5458,7 @@
         <v>152</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>199</v>
@@ -5466,10 +5470,10 @@
         <v>38</v>
       </c>
       <c r="L46" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M46" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N46" s="7"/>
       <c r="O46" s="4"/>
@@ -5478,16 +5482,16 @@
     </row>
     <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -5495,7 +5499,7 @@
         <v>152</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>62</v>
@@ -5507,10 +5511,10 @@
         <v>38</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="9"/>
@@ -5519,16 +5523,16 @@
     </row>
     <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -5536,7 +5540,7 @@
         <v>152</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>37</v>
@@ -5548,10 +5552,10 @@
         <v>28</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="9"/>
@@ -5560,16 +5564,16 @@
     </row>
     <row r="49" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E49" s="9"/>
       <c r="F49" s="12"/>
@@ -5577,7 +5581,7 @@
         <v>152</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>199</v>
@@ -5589,10 +5593,10 @@
         <v>62</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="9"/>
@@ -5601,16 +5605,16 @@
     </row>
     <row r="50" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="12"/>
@@ -5618,7 +5622,7 @@
         <v>26</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>121</v>
@@ -5630,10 +5634,10 @@
         <v>38</v>
       </c>
       <c r="L50" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M50" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="9"/>
@@ -5642,16 +5646,16 @@
     </row>
     <row r="51" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
@@ -5659,7 +5663,7 @@
         <v>26</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>62</v>
@@ -5671,10 +5675,10 @@
         <v>38</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M51" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="9"/>
@@ -5683,16 +5687,16 @@
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E52" s="9"/>
       <c r="F52" s="12"/>
@@ -5700,7 +5704,7 @@
         <v>26</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>135</v>
@@ -5712,10 +5716,10 @@
         <v>38</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="9"/>
@@ -5724,16 +5728,16 @@
     </row>
     <row r="53" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E53" s="9"/>
       <c r="F53" s="12"/>
@@ -5741,7 +5745,7 @@
         <v>26</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>121</v>
@@ -5753,10 +5757,10 @@
         <v>38</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="9"/>
@@ -5765,16 +5769,16 @@
     </row>
     <row r="54" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E54" s="9"/>
       <c r="F54" s="12"/>
@@ -5782,7 +5786,7 @@
         <v>26</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>37</v>
@@ -5794,10 +5798,10 @@
         <v>28</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="9"/>
@@ -5806,16 +5810,16 @@
     </row>
     <row r="55" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E55" s="9"/>
       <c r="F55" s="3"/>
@@ -5823,7 +5827,7 @@
         <v>26</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>76</v>
@@ -5835,10 +5839,10 @@
         <v>148</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="9"/>
@@ -5847,16 +5851,16 @@
     </row>
     <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
@@ -5864,7 +5868,7 @@
         <v>152</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>62</v>
@@ -5876,10 +5880,10 @@
         <v>38</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="9"/>
@@ -5888,16 +5892,16 @@
     </row>
     <row r="57" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E57" s="9"/>
       <c r="F57" s="12"/>
@@ -5905,7 +5909,7 @@
         <v>152</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>135</v>
@@ -5917,10 +5921,10 @@
         <v>38</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="9"/>
@@ -5929,16 +5933,16 @@
     </row>
     <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -5946,7 +5950,7 @@
         <v>152</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>53</v>
@@ -5958,10 +5962,10 @@
         <v>53</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N58" s="3"/>
       <c r="O58" s="9"/>
@@ -5970,16 +5974,16 @@
     </row>
     <row r="59" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="9"/>
@@ -5987,7 +5991,7 @@
         <v>152</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>53</v>
@@ -5999,10 +6003,10 @@
         <v>53</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="9"/>
